--- a/Plan/Table/TestData/05.TagData.xlsx
+++ b/Plan/Table/TestData/05.TagData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7DA948A-4A5D-4890-9476-CD60F0B4B3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{087464DA-0B22-4D30-8366-3EC0ECEBF312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{5B128965-9624-419E-A4F5-274D40A7596C}"/>
+    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{2667EA21-470C-462C-A8AF-123CACD0F7FD}"/>
   </bookViews>
   <sheets>
     <sheet name="05.TagData" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>ID</t>
   </si>
@@ -59,88 +62,58 @@
     <t>Tag_Des_1</t>
   </si>
   <si>
-    <t>Card_Tag_001</t>
-  </si>
-  <si>
     <t>Tag_Name_2</t>
   </si>
   <si>
     <t>Tag_Des_2</t>
   </si>
   <si>
-    <t>Card_Tag_002</t>
-  </si>
-  <si>
     <t>Tag_Name_3</t>
   </si>
   <si>
     <t>Tag_Des_3</t>
   </si>
   <si>
-    <t>Card_Tag_003</t>
-  </si>
-  <si>
     <t>Tag_Name_4</t>
   </si>
   <si>
     <t>Tag_Des_4</t>
   </si>
   <si>
-    <t>Card_Tag_004</t>
-  </si>
-  <si>
     <t>Tag_Name_5</t>
   </si>
   <si>
     <t>Tag_Des_5</t>
   </si>
   <si>
-    <t>Card_Tag_005</t>
-  </si>
-  <si>
     <t>Tag_Name_6</t>
   </si>
   <si>
     <t>Tag_Des_6</t>
   </si>
   <si>
-    <t>Card_Tag_006</t>
-  </si>
-  <si>
     <t>Tag_Name_7</t>
   </si>
   <si>
     <t>Tag_Des_7</t>
   </si>
   <si>
-    <t>Card_Tag_007</t>
-  </si>
-  <si>
     <t>Tag_Name_8</t>
   </si>
   <si>
     <t>Tag_Des_8</t>
   </si>
   <si>
-    <t>Card_Tag_008</t>
-  </si>
-  <si>
     <t>Tag_Name_9</t>
   </si>
   <si>
     <t>Tag_Des_9</t>
   </si>
   <si>
-    <t>Card_Tag_009</t>
-  </si>
-  <si>
     <t>Tag_Name_10</t>
   </si>
   <si>
     <t>Tag_Des_10</t>
-  </si>
-  <si>
-    <t>Card_Tag_010</t>
   </si>
   <si>
     <t>Value_1</t>
@@ -553,7 +526,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF8E1AD-77FA-4910-AB94-AAE087C8252B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{574D0231-29E4-40B9-8D66-53417C8ECA3A}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -574,34 +548,34 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="I1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="J1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="K1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="N1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="O1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -617,8 +591,8 @@
       <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
-        <v>7</v>
+      <c r="E2">
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -659,13 +633,13 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
+      <c r="E3">
+        <v>0</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -706,13 +680,13 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -753,13 +727,13 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -800,13 +774,13 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -847,13 +821,13 @@
         <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
       </c>
       <c r="F7">
         <v>500</v>
@@ -894,13 +868,13 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -941,13 +915,13 @@
         <v>128</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
+        <v>20</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -988,13 +962,13 @@
         <v>256</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1035,13 +1009,13 @@
         <v>512</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
-        <v>34</v>
+        <v>24</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>

--- a/Plan/Table/TestData/05.TagData.xlsx
+++ b/Plan/Table/TestData/05.TagData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{087464DA-0B22-4D30-8366-3EC0ECEBF312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80BE17D7-43BE-4FB8-B1F3-E1EED19977B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19500" yWindow="3720" windowWidth="14505" windowHeight="13485" xr2:uid="{2667EA21-470C-462C-A8AF-123CACD0F7FD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{35D87F63-45BE-4A9D-BB6D-2C4BF576A753}"/>
   </bookViews>
   <sheets>
     <sheet name="05.TagData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
@@ -62,6 +62,9 @@
     <t>Tag_Des_1</t>
   </si>
   <si>
+    <t>Tag_Weapon.png</t>
+  </si>
+  <si>
     <t>Tag_Name_2</t>
   </si>
   <si>
@@ -74,24 +77,36 @@
     <t>Tag_Des_3</t>
   </si>
   <si>
+    <t>Tag_Flame.png</t>
+  </si>
+  <si>
     <t>Tag_Name_4</t>
   </si>
   <si>
     <t>Tag_Des_4</t>
   </si>
   <si>
+    <t>Tag_Ice.png</t>
+  </si>
+  <si>
     <t>Tag_Name_5</t>
   </si>
   <si>
     <t>Tag_Des_5</t>
   </si>
   <si>
+    <t>Tag_Electric.png</t>
+  </si>
+  <si>
     <t>Tag_Name_6</t>
   </si>
   <si>
     <t>Tag_Des_6</t>
   </si>
   <si>
+    <t>Tag_Tool.png</t>
+  </si>
+  <si>
     <t>Tag_Name_7</t>
   </si>
   <si>
@@ -104,16 +119,25 @@
     <t>Tag_Des_8</t>
   </si>
   <si>
+    <t>Tag_Consumable.png</t>
+  </si>
+  <si>
     <t>Tag_Name_9</t>
   </si>
   <si>
     <t>Tag_Des_9</t>
   </si>
   <si>
+    <t>Tag_Mana.png</t>
+  </si>
+  <si>
     <t>Tag_Name_10</t>
   </si>
   <si>
     <t>Tag_Des_10</t>
+  </si>
+  <si>
+    <t>Tag_Magic.png</t>
   </si>
   <si>
     <t>Value_1</t>
@@ -526,8 +550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{574D0231-29E4-40B9-8D66-53417C8ECA3A}">
-  <sheetPr codeName="Sheet1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68D1CB3E-2F28-4917-AB11-669D4377DBEC}">
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -548,34 +571,34 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="N1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="O1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -591,8 +614,8 @@
       <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="E2">
-        <v>0</v>
+      <c r="E2" t="s">
+        <v>7</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -633,10 +656,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -680,13 +703,13 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -727,13 +750,13 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -774,13 +797,13 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -821,13 +844,13 @@
         <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
       </c>
       <c r="F7">
         <v>500</v>
@@ -868,10 +891,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -915,13 +938,13 @@
         <v>128</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -962,13 +985,13 @@
         <v>256</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1009,13 +1032,13 @@
         <v>512</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
       </c>
       <c r="F11">
         <v>0</v>
